--- a/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/enerji_karsilastirma.xlsx
+++ b/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/enerji_karsilastirma.xlsx
@@ -813,7 +813,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
@@ -1001,6 +1001,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1385,7 +1388,7 @@
     <row r="1" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
       <c r="A1" s="62" t="inlineStr">
         <is>
-          <t>PlanetDISK® DBD TEKNOLOJİSİ İLE AKTİF ÇAMUR SİSTEMİ ENERJİ KARŞILAŞTIRMA TABLOSU</t>
+          <t>Enerji ve İşletme Maliyeti Karşılaştırma Analizi</t>
         </is>
       </c>
       <c r="B1" s="50" t="n"/>
@@ -1439,7 +1442,7 @@
     <row r="4" ht="15" customHeight="1" thickTop="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MX 1 Unit Number</t>
+          <t>Ünite / Ekipman Adedi</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -1452,7 +1455,7 @@
       </c>
       <c r="D4" s="69" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Ünite / Ekipman Adedi</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -1475,7 +1478,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>MX 1 Motor Power</t>
+          <t>Birim Motor Gücü (kW)</t>
         </is>
       </c>
       <c r="B5" s="54" t="inlineStr">
@@ -1486,12 +1489,12 @@
       <c r="C5" s="44" t="n"/>
       <c r="D5" s="70" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Birim Motor Gücü (kW)</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>2,00</t>
+          <t>3,00</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -1501,7 +1504,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>2,20</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -1513,7 +1516,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Total Power</t>
+          <t>Toplam Kurulu Güç</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
@@ -1528,12 +1531,12 @@
       </c>
       <c r="D6" s="70" t="inlineStr">
         <is>
-          <t>Total Power</t>
+          <t>Toplam Kurulu Güç</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>2,00</t>
+          <t>3,00</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -1543,7 +1546,7 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>2,20</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
@@ -1555,7 +1558,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Power Consumption</t>
+          <t>Anlık Güç Tüketim Oranı (%)</t>
         </is>
       </c>
       <c r="B7" s="43" t="inlineStr">
@@ -1566,7 +1569,7 @@
       <c r="C7" s="44" t="n"/>
       <c r="D7" s="70" t="inlineStr">
         <is>
-          <t>Power Consumption</t>
+          <t>Anlık Güç Tüketim Oranı (%)</t>
         </is>
       </c>
       <c r="E7" s="47" t="inlineStr">
@@ -1585,7 +1588,7 @@
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Total Actual Power to be used</t>
+          <t>Kullanılacak Gerçek Net Güç</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
@@ -1600,12 +1603,12 @@
       </c>
       <c r="D8" s="70" t="inlineStr">
         <is>
-          <t>Total Actual Power to be used</t>
+          <t>Kullanılacak Gerçek Net Güç</t>
         </is>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>1,80</t>
+          <t>2,70</t>
         </is>
       </c>
       <c r="F8" s="18" t="inlineStr">
@@ -1615,7 +1618,7 @@
       </c>
       <c r="G8" s="19" t="inlineStr">
         <is>
-          <t>1,98</t>
+          <t>0,50</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -1627,49 +1630,49 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Electricity Price</t>
+          <t>Elektrik Birim Fiyatı (€/kWh)</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>7,15</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ₺/kW</t>
+          <t xml:space="preserve"> €/kW</t>
         </is>
       </c>
       <c r="D9" s="70" t="inlineStr">
         <is>
-          <t>Electricity Price</t>
+          <t>Elektrik Birim Fiyatı (€/kWh)</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>7,15</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ₺/kW</t>
+          <t xml:space="preserve"> €/kW</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t>7,15</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ₺/kW</t>
+          <t xml:space="preserve"> €/kW</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Daily Working Time</t>
+          <t>Günlük Çalışma Süresi (saat)</t>
         </is>
       </c>
       <c r="B10" s="14" t="n">
@@ -1682,7 +1685,7 @@
       </c>
       <c r="D10" s="70" t="inlineStr">
         <is>
-          <t>Daily Working Time</t>
+          <t>Günlük Çalışma Süresi (saat)</t>
         </is>
       </c>
       <c r="E10" s="14" t="n">
@@ -1705,7 +1708,7 @@
     <row r="11" ht="15" customHeight="1" thickBot="1">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>Yearly Working Time</t>
+          <t>Yıllık Çalışma Süresi</t>
         </is>
       </c>
       <c r="B11" s="24" t="n">
@@ -1718,7 +1721,7 @@
       </c>
       <c r="D11" s="71" t="inlineStr">
         <is>
-          <t>Yearly Working Time</t>
+          <t>Yıllık Çalışma Süresi</t>
         </is>
       </c>
       <c r="E11" s="24" t="n">
@@ -1741,49 +1744,37 @@
     <row r="12" ht="25.2" customHeight="1" thickBot="1" thickTop="1">
       <c r="A12" s="29" t="inlineStr">
         <is>
-          <t>PlanetDISK® Ünitesi Enerji Gideri</t>
+          <t>Yıllık Tüketim Maliyeti</t>
         </is>
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>379 ₺</t>
-        </is>
-      </c>
-      <c r="C12" s="31" t="inlineStr">
-        <is>
-          <t>/yıl</t>
-        </is>
-      </c>
+          <t>379 € / yıl</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="inlineStr"/>
       <c r="D12" s="32" t="inlineStr">
         <is>
-          <t>Klasik Aktif Çamur Enerji Gideri</t>
+          <t>Klasik Aktif Çamur Sistemi Enerji Gideri</t>
         </is>
       </c>
       <c r="E12" s="33" t="inlineStr">
         <is>
-          <t>2.050 ₺</t>
-        </is>
-      </c>
-      <c r="F12" s="34" t="inlineStr">
-        <is>
-          <t>/yıl</t>
-        </is>
-      </c>
-      <c r="G12" s="35" t="inlineStr">
-        <is>
-          <t>376 ₺</t>
-        </is>
-      </c>
-      <c r="H12" s="36" t="inlineStr">
-        <is>
-          <t>/yıl</t>
-        </is>
-      </c>
+          <t>3.075 € / yıl</t>
+        </is>
+      </c>
+      <c r="F12" s="34" t="n"/>
+      <c r="G12" s="72" t="inlineStr">
+        <is>
+          <t>94 € / yıl</t>
+        </is>
+      </c>
+      <c r="H12" s="53" t="n"/>
     </row>
     <row r="13" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
       <c r="A13" s="64" t="inlineStr">
         <is>
-          <t>PlanetDISK® diğer atıksu arıtma sistemleri ile karşılaştırıldığında, enerji tasarrufu</t>
+          <t>"Klasik Aktif Çamur Sistemi"'ne Kıyasla Yıllık Enerji Tasarrufu:</t>
         </is>
       </c>
       <c r="B13" s="50" t="n"/>
@@ -1791,7 +1782,7 @@
       <c r="D13" s="50" t="n"/>
       <c r="E13" s="67" t="inlineStr">
         <is>
-          <t>2.046 ₺ / yıl</t>
+          <t>2.789 € / yıl</t>
         </is>
       </c>
       <c r="F13" s="41" t="n"/>
@@ -1801,7 +1792,7 @@
     <row r="14" ht="15" customHeight="1" thickTop="1">
       <c r="A14" s="65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tasarruf tutarı 10 yılda </t>
+          <t>Sistem Ömrü Boyunca 10 Yıllık Elektrik Kazancı:</t>
         </is>
       </c>
       <c r="B14" s="66" t="n"/>
@@ -1809,7 +1800,7 @@
       <c r="D14" s="66" t="n"/>
       <c r="E14" s="40" t="inlineStr">
         <is>
-          <t>20.464 ₺ / 10 yıl</t>
+          <t>27.895 € / 10 yıl</t>
         </is>
       </c>
       <c r="F14" s="41" t="n"/>
@@ -1819,7 +1810,7 @@
     <row r="15" ht="34.2" customHeight="1" thickBot="1">
       <c r="A15" s="55" t="inlineStr">
         <is>
-          <t>Blower ve Difüzör Bakım Masraflarıyla birlikte bu rakam</t>
+          <t>Blower, Difüzör Yenileme ve Bakım Maliyetleri Dahil Yaklaşık Toplam Tasarruf (10 Yıl)</t>
         </is>
       </c>
       <c r="B15" s="56" t="n"/>
@@ -1827,7 +1818,7 @@
       <c r="D15" s="56" t="n"/>
       <c r="E15" s="57" t="inlineStr">
         <is>
-          <t>21.000 ₺</t>
+          <t>28.000 €</t>
         </is>
       </c>
       <c r="F15" s="58" t="n"/>
@@ -1836,8 +1827,9 @@
     </row>
     <row r="16" ht="15" customHeight="1" thickTop="1"/>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="E14:H14"/>
+    <mergeCell ref="G12:H12"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="E7:F7"/>
